--- a/docs/data/chimera_battle_ctb_redesign_v02_clean.xlsx
+++ b/docs/data/chimera_battle_ctb_redesign_v02_clean.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -795,11 +795,11 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>行動開始MP回復</t>
+          <t>戦闘後MP回復</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -808,73 +808,73 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>自分の手番開始時</t>
+          <t>戦闘終了(勝利)後にまとめて回復</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>MP0技との役割分担</t>
+          <t>戦闘中はMPを使い切る緊張感を保つ</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>防御追加MP回復</t>
+          <t>CT短縮下限</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>6</v>
+        <v>0.45</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>倍率</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>防御成功時</t>
+          <t>全補正後の最低CT倍率</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>守りが攻めにつながる</t>
+          <t>無限行動防止</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>CT短縮下限</t>
+          <t>CT遅延上限</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>倍率</t>
+          <t>割合</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>全補正後の最低CT倍率</t>
+          <t>1回で押し戻せる最大量</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>無限行動防止</t>
+          <t>永久拘束防止</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>CT遅延上限</t>
+          <t>敵遅延耐性_通常</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
@@ -883,23 +883,23 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1回で押し戻せる最大量</t>
+          <t>通常敵</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>永久拘束防止</t>
+          <t>CT操作を気持ちよく</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>敵遅延耐性_通常</t>
+          <t>敵遅延耐性_エリート</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -908,23 +908,23 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>通常敵</t>
+          <t>エリート</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>CT操作を気持ちよく</t>
+          <t>完全拘束防止</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>敵遅延耐性_エリート</t>
+          <t>敵遅延耐性_ボス</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -933,87 +933,62 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>エリート</t>
+          <t>ボス</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>完全拘束防止</t>
+          <t>遅延ビルドは有効だが弱まる</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>敵遅延耐性_ボス</t>
+          <t>行動順表示</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>割合</t>
+          <t>件</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>ボス</t>
+          <t>未来の予告</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>遅延ビルドは有効だが弱まる</t>
+          <t>CTB判断材料</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>行動順表示</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>8</v>
+          <t>敵意図表示</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>件</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>未来の予告</t>
+          <t>次行動の種類を予告</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>CTB判断材料</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>敵意図表示</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>次行動の種類を予告</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>CTB対策判断</t>
         </is>
@@ -1416,7 +1391,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>次被ダメージ50%軽減+MP回復</t>
+          <t>次被ダメージ50%軽減</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr"/>
@@ -1492,7 +1467,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>何もせず次手番を早めMP+4</t>
+          <t>何もせず次手番を早める</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr"/>

--- a/docs/data/chimera_battle_ctb_redesign_v02_clean.xlsx
+++ b/docs/data/chimera_battle_ctb_redesign_v02_clean.xlsx
@@ -15,6 +15,7 @@
     <sheet name="シナジー" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="状態異常" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="代表ビルド" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="融合" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'README'!$A$1:$B$8</definedName>
@@ -17930,4 +17931,584 @@
   <autoFilter ref="A1:H21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="52" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>融合名</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>アイコン</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>素材タグA</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>素材タグB</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>カテゴリ</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>継承タグ</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>効果</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FUS001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>灼熱牙</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>炎</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>攻撃</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>口</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>炎/攻撃</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>全攻撃威力+14% / 命中時に炎上(3,2ターン)を付与</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>炎の器官と攻撃器官を融合した顎。攻撃力そのものを底上げし、当たるたび相手を燃やす。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FUS002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>猛毒腺</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>☠️</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>毒</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>状態異常</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>器官</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>毒/状態異常</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>命中時に毒(3,3ターン)を付与 / 自分が与える毒の量+2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>毒腺と状態異常器官の融合。毒を撒く頻度と濃度の両方が上がる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FUS003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>疾風装甲</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>高速</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>防御</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>胴</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>高速/防御</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>速度+8 / 防御力+3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>軽量装甲。速さを保ったまま打たれ強さを足す、CTBで最も潰しの効く組み合わせ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FUS004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>時喰核</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>時間</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>コア</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>時間/MP</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>遅延効果量+25% / 最大MP+15</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>時間干渉器官と魔力嚢の融合核。遅延を撃ち続けるための燃料と威力を同時に得る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FUS005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>暴走再生心</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>💢</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>暴走</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>再生</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>心臓</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>暴走/再生</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>HP50%以下でCT-15% / 手番開始時にHP+3</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>暴走心臓に再生組織を編み込んだもの。追い詰められるほど速くなり、じわじわ立て直す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FUS006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>反射棘甲</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>🌵</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>反撃</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>重量</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>胴</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>反撃/重量</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>被弾するたびダメージの18%を反射 / 防御力+4</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>棘甲と重装甲の融合。殴られること自体が攻撃手段になる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FUS007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>捕食顎</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>🦈</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>捕食</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>吸血</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>口</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>捕食/吸血</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>吸血の回復量+20% / 敵撃破時にMP+8</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>捕食器官と吸血口の融合。倒すほど息を吹き返す、長期戦向けの顎。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FUS008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>多重腕</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>🦑</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>多段</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>多腕</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>腕</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>多段/多腕</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>多段コマンドのヒット数+1 / 軽量攻撃の威力+12%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>腕を束ねて多重化したもの。手数で押し切るビルドの中核。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FUS009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>解析角</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>🧠</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>知性</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>貫通</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>角</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>知性/貫通</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>補助コマンドのCT-15% / 敵防御力の25%を無視</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>知性器官と穿孔角の融合。相手の守りを読み切って、準備も速くなる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FUS010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>雷光眼</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>雷</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>高速</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>目</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>雷/高速</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>命中率+12% / 全行動のCT-8%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>雷を宿した複眼。見てから動くまでが速くなる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FUS000</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>融合塊</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>🧫</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>器官</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>器官</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>最大HP+10 / 全攻撃威力+6%</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>噛み合わせの悪い2部位を無理やり繋いだ塊。尖ってはいないが、無駄にはならない。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/docs/data/chimera_battle_ctb_redesign_v02_clean.xlsx
+++ b/docs/data/chimera_battle_ctb_redesign_v02_clean.xlsx
@@ -16,6 +16,7 @@
     <sheet name="状態異常" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="代表ビルド" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="融合" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="難易度" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'README'!$A$1:$B$8</definedName>
@@ -550,6 +551,357 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="50" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>プリセット</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>既定</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>敵HP倍率_通常</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>敵HP倍率_エリート</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>敵HP倍率_ボス</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>敵攻撃力倍率_通常</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>敵攻撃力倍率_エリート</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>敵攻撃力倍率_ボス</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>敵防御力倍率</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>敵回避率倍率</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>プレイヤーHP倍率</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>戦闘後HP回復率</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>戦闘後MP回復倍率</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>レア報酬加算_戦ごと</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DIF001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>やさしい</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>初見・UI確認向け。通常戦はほぼ消耗しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DIF002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ふつう</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>既定。通常戦は消耗、エリートは山場、ボスはプレイヤーHPの約3倍。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DIF003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>むずかしい</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>ビルドが噛み合わないと通常戦でも落ちる。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/docs/data/chimera_battle_ctb_redesign_v02_clean.xlsx
+++ b/docs/data/chimera_battle_ctb_redesign_v02_clean.xlsx
@@ -18291,18 +18291,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
-    <col width="52" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="56" customWidth="1" min="10" max="10"/>
+    <col width="52" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18323,30 +18325,40 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>素材タグA</t>
+          <t>レア度</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>素材タグB</t>
+          <t>条件種別</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>素材A</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>素材B</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>カテゴリ</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>継承タグ</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>効果</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>説明</t>
         </is>
@@ -18355,7 +18367,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FUS001</t>
+          <t>FUS101</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -18370,39 +18382,49 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>タグ</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>炎</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>攻撃</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>口</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>炎/攻撃</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>全攻撃威力+14% / 命中時に炎上(3,2ターン)を付与</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>炎の器官と攻撃器官を融合した顎。攻撃力そのものを底上げし、当たるたび相手を燃やす。</t>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>全攻撃威力+18% / 命中時に炎上(4,3ターン)</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>炎の器官と攻撃器官を噛み合わせた顎。素の火炎頭より火力も燃焼も上。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FUS002</t>
+          <t>FUS102</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -18417,39 +18439,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>タグ</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>毒</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>状態異常</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>器官</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>毒/状態異常</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>命中時に毒(3,3ターン)を付与 / 自分が与える毒の量+2</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>毒腺と状態異常器官の融合。毒を撒く頻度と濃度の両方が上がる。</t>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>命中時に毒(4,4ターン) / 与える毒の量+3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>毒腺を二重化したもの。毒の乗りが速く、濃くなる。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FUS003</t>
+          <t>FUS103</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -18464,39 +18496,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>タグ</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>高速</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>防御</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>胴</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>高速/防御</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>速度+8 / 防御力+3</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>軽量装甲。速さを保ったまま打たれ強さを足す、CTBで最も潰しの効く組み合わせ。</t>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>速度+12 / 防御力+6 / 回避率+6%</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>軽さを殺さない装甲。素の防具より硬く、素の脚より速く、そのうえ避ける。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FUS004</t>
+          <t>FUS104</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -18511,30 +18553,40 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>タグ</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>時間</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>MP</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>コア</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>時間/MP</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>遅延効果量+25% / 最大MP+15</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>遅延効果量+30% / 最大MP+18</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>時間干渉器官と魔力嚢の融合核。遅延を撃ち続けるための燃料と威力を同時に得る。</t>
         </is>
@@ -18543,321 +18595,513 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FUS005</t>
+          <t>FUS105</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>暴走再生心</t>
+          <t>反射棘甲</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>💢</t>
+          <t>🌵</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>暴走</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>再生</t>
+          <t>タグ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>心臓</t>
+          <t>反撃</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>暴走/再生</t>
+          <t>重量</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>HP50%以下でCT-15% / 手番開始時にHP+3</t>
+          <t>胴</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>暴走心臓に再生組織を編み込んだもの。追い詰められるほど速くなり、じわじわ立て直す。</t>
+          <t>反撃/重量</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>被弾するたびダメージの26%を反射 / 防御力+6 / 被弾時18%で反撃(威力0.6倍)</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>棘と重装甲を編んだもの。殴られること自体が攻撃手段になり、時には殴り返す。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FUS006</t>
+          <t>FUS106</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>反射棘甲</t>
+          <t>捕食顎</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🌵</t>
+          <t>🦈</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>反撃</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>重量</t>
+          <t>タグ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>胴</t>
+          <t>捕食</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>反撃/重量</t>
+          <t>吸血</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>被弾するたびダメージの18%を反射 / 防御力+4</t>
+          <t>口</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>棘甲と重装甲の融合。殴られること自体が攻撃手段になる。</t>
+          <t>捕食/吸血</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>吸血の回復量+25% / 敵撃破時にMP+10</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>捕食器官と吸血口の融合。倒すほど息を吹き返す。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FUS007</t>
+          <t>FUS201</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>捕食顎</t>
+          <t>多重腕</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🦈</t>
+          <t>🦑</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>捕食</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>吸血</t>
+          <t>タグ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>口</t>
+          <t>多腕</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>捕食/吸血</t>
+          <t>多段</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>吸血の回復量+20% / 敵撃破時にMP+8</t>
+          <t>腕</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>捕食器官と吸血口の融合。倒すほど息を吹き返す、長期戦向けの顎。</t>
+          <t>多段/多腕</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>多段コマンドのヒット数+1 / 軽量攻撃の威力+18% / 速度+4</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>腕を束ねて多重化したもの。手数で押し切るビルドの中核。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FUS008</t>
+          <t>FUS202</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>多重腕</t>
+          <t>解析角</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🦑</t>
+          <t>🧠</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>多段</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>多腕</t>
+          <t>タグ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>腕</t>
+          <t>知性</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>多段/多腕</t>
+          <t>貫通</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>多段コマンドのヒット数+1 / 軽量攻撃の威力+12%</t>
+          <t>角</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>腕を束ねて多重化したもの。手数で押し切るビルドの中核。</t>
+          <t>知性/貫通</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>補助コマンドのCT-20% / 敵防御力の35%を無視 / 命中率+8%</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>知性器官と穿孔角の融合。守りを読み切り、準備も速くなる。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FUS009</t>
+          <t>FUS203</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>解析角</t>
+          <t>雷光眼</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🧠</t>
+          <t>⚡</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>知性</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>貫通</t>
+          <t>タグ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>角</t>
+          <t>雷</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>知性/貫通</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>補助コマンドのCT-15% / 敵防御力の25%を無視</t>
+          <t>目</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>知性器官と穿孔角の融合。相手の守りを読み切って、準備も速くなる。</t>
+          <t>雷/高速</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>命中率+15% / 全行動のCT-11% / 命中時に感電(2,3ターン)</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>雷を宿した複眼。見てから動くまでが速い。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FUS010</t>
+          <t>FUS204</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>雷光眼</t>
+          <t>暴走再生心</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>💢</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>雷</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>タグ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>目</t>
+          <t>暴走</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>雷/高速</t>
+          <t>再生</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>命中率+12% / 全行動のCT-8%</t>
+          <t>心臓</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>雷を宿した複眼。見てから動くまでが速くなる。</t>
+          <t>暴走/再生</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>HP50%以下でCT-20% / 手番開始時にHP+5 / 最大HP+15</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>暴走心臓に再生組織を編み込んだもの。追い詰められるほど速く、しぶとい。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FUS000</t>
+          <t>FUS301</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>融合塊</t>
+          <t>終焉の顎</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🧫</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+          <t>🐲</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>部位</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>器官</t>
+          <t>PRT013</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>器官</t>
+          <t>PRT028</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>最大HP+10 / 全攻撃威力+6%</t>
+          <t>口</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>噛み合わせの悪い2部位を無理やり繋いだ塊。尖ってはいないが、無駄にはならない。</t>
+          <t>処刑/多段/攻撃</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>多段コマンドのヒット数+1 / 全攻撃威力+22% / HP30%以下の敵へ威力2.0倍 / 敵撃破時に次の行動が早まる+25%</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>処刑眼・極と多腕・零を融合した顎。弱った敵を確実に噛み切る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FUS302</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>時空の王冠</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>👑</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>部位</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>PRT055</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>PRT077</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>コア</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>時間/MP/妨害</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>遅延効果量+45% / 最大MP+30 / 補助コマンドのCT-25%</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>時間尾・極と魔力嚢・零を編み込んだ核。時間そのものを資源にする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FUS303</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>雷神角</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>🌩️</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>部位</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>PRT069</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>PRT068</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>角</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>雷/貫通/状態異常</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>敵防御力の45%を無視 / 全攻撃威力+20% / 命中時に感電(3,3ターン) / 速度+6</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>雷角・極に穿孔角・異を貫かせたもの。硬い相手ほどよく通る。</t>
         </is>
       </c>
     </row>

--- a/docs/data/chimera_battle_ctb_redesign_v02_clean.xlsx
+++ b/docs/data/chimera_battle_ctb_redesign_v02_clean.xlsx
@@ -557,25 +557,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-    <col width="50" customWidth="1" min="16" max="16"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="46" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -656,6 +658,16 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>エリアHP倍率</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>エリア威力倍率</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>説明</t>
         </is>
       </c>
@@ -734,6 +746,16 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>0.75/1.0/1.3/1.6</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0.7/0.9/1.15/1.35</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>初見・UI確認向け。通常戦はほぼ消耗しない。</t>
         </is>
       </c>
@@ -816,6 +838,16 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>0.85/1.1/1.45/1.85</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0.8/1.0/1.25/1.5</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>既定。通常戦は消耗、エリートは山場、ボスはプレイヤーHPの約3倍。</t>
         </is>
       </c>
@@ -893,6 +925,16 @@
         </is>
       </c>
       <c r="P4" t="inlineStr">
+        <is>
+          <t>0.95/1.2/1.6/2.05</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0.9/1.1/1.4/1.65</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>ビルドが噛み合わないと通常戦でも落ちる。</t>
         </is>
@@ -6094,23 +6136,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O81"/>
+  <dimension ref="A1:O86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
@@ -6192,4916 +6234,5195 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>PRT001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>予知脳</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>頭</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>知性</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>時間</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>敵意図を詳細化</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>CTプレビュー+2</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
         <is>
           <t>遅延/加速+15%</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
         <is>
           <t>CT操作</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>PRT002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>火炎頭</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>頭</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>炎</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>攻撃</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>攻撃小UP</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
         <is>
           <t>攻撃に炎上付与</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>炎</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
         <is>
           <t>炎上</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>PRT003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>狂戦頭</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>頭</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>暴走</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>重量</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>攻撃UP</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>低HP時CT-12%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
         <is>
           <t>強打強化</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
         <is>
           <t>防御DOWN</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>暴走</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>PRT004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>予知脳・改</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>頭</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>知性</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>時間</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>敵意図を詳細化</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>CTプレビュー+2</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
         <is>
           <t>遅延/加速+15%</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
         <is>
           <t>同タグ部位2個以上で効果強化</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
         <is>
           <t>CT操作</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>PRT005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>火炎頭・異</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>頭</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>炎</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>攻撃</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>攻撃小UP</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
         <is>
           <t>攻撃に炎上付与</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>炎</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>同タグ部位2個以上で効果強化</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
         <is>
           <t>炎上</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>PRT006</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>狂戦頭・極</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>頭</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>暴走</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>重量</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>攻撃UP</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>低HP時CT-12%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
         <is>
           <t>強打強化</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
         <is>
           <t>特定条件で戦闘ルールを変更</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>防御DOWN</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>暴走</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>PRT007</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>予知脳・零</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>頭</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>知性</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>時間</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>敵意図を詳細化</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>CTプレビュー+2</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
         <is>
           <t>遅延/加速+15%</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
         <is>
           <t>特定条件で戦闘ルールを変更</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
         <is>
           <t>CT操作</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>PRT008</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>時喰い眼</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>目</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>頭</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>時間</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>知性</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
         <is>
           <t>敵遅延+20%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
         <is>
           <t>時間系強化</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
         <is>
           <t>CT妨害</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>PRT009</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>複眼</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>目</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>頭</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>多眼</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>高速</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>命中UP</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>軽量CT-5%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
         <is>
           <t>多段命中UP</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
         <is>
           <t>高速</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>PRT010</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>処刑眼</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>目</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>頭</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>処刑</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>知性</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>低HP敵への威力UP</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
         <is>
           <t>処刑強化</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
         <is>
           <t>処刑</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>PRT011</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>時喰い眼・改</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>目</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>頭</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>時間</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>知性</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
         <is>
           <t>敵遅延+20%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
         <is>
           <t>時間系強化</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
         <is>
           <t>同タグ部位2個以上で効果強化</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
         <is>
           <t>CT妨害</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>PRT012</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>複眼・異</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>目</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>頭</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>多眼</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>高速</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>命中UP</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>軽量CT-5%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
         <is>
           <t>多段命中UP</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
         <is>
           <t>同タグ部位2個以上で効果強化</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
         <is>
           <t>高速</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>PRT013</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>処刑眼・極</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>目</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>頭</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>処刑</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>知性</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>低HP敵への威力UP</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
         <is>
           <t>処刑強化</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
         <is>
           <t>特定条件で戦闘ルールを変更</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
         <is>
           <t>処刑</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>PRT014</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>時喰い眼・零</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>目</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>頭</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>時間</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>知性</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
         <is>
           <t>敵遅延+20%</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
         <is>
           <t>時間系強化</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
         <is>
           <t>特定条件で戦闘ルールを変更</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
         <is>
           <t>CT妨害</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>PRT015</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>血吸口</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>口</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>頭</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>吸血</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>捕食</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
         <is>
           <t>吸血量+30%</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
         <is>
           <t>吸血</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>PRT016</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>毒腺口</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>口</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>頭</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>毒</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>状態異常</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
         <is>
           <t>毒付与+1</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>毒</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
         <is>
           <t>毒</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>PRT017</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>咆哮口</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>口</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>頭</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>時間</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>妨害</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
         <is>
           <t>最大MP+8</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>咆哮MP-3</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
         <is>
           <t>CT妨害</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>PRT018</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>血吸口・改</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>口</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>頭</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>吸血</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>捕食</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
         <is>
           <t>吸血量+30%</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
         <is>
           <t>同タグ部位2個以上で効果強化</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
         <is>
           <t>吸血</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>PRT019</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>毒腺口・異</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>口</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>頭</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>毒</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>状態異常</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
         <is>
           <t>毒付与+1</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>毒</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>同タグ部位2個以上で効果強化</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
         <is>
           <t>毒</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>PRT020</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>咆哮口・極</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>口</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>頭</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>時間</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>妨害</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
         <is>
           <t>最大MP+8</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>咆哮MP-3</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
         <is>
           <t>特定条件で戦闘ルールを変更</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
         <is>
           <t>CT妨害</t>
         </is>
       </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>PRT021</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>血吸口・零</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>口</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>頭</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>吸血</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>捕食</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
         <is>
           <t>吸血量+30%</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
         <is>
           <t>特定条件で戦闘ルールを変更</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
         <is>
           <t>吸血</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>PRT022</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>多腕</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>腕</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>多腕</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>多段</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>通常攻撃+1Hit</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
         <is>
           <t>連撃強化</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
         <is>
           <t>多腕</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>PRT023</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>豪腕</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>腕</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>重量</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>攻撃</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>攻撃UP</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>重量CTペナルティ-10%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
         <is>
           <t>強打強化</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
         <is>
           <t>軽量CT+5%</t>
         </is>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>重量</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>PRT024</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>反射腕</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>腕</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>反撃</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>防御</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>防御UP</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
         <is>
           <t>カウンター強化</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
         <is>
           <t>反撃</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>PRT025</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>多腕・改</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>腕</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>多腕</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>多段</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>通常攻撃+1Hit</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
         <is>
           <t>連撃強化</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
         <is>
           <t>同タグ部位2個以上で効果強化</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
         <is>
           <t>多腕</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>PRT026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>豪腕・異</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>腕</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>重量</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>攻撃</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>攻撃UP</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>重量CTペナルティ-10%</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
         <is>
           <t>強打強化</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
         <is>
           <t>同タグ部位2個以上で効果強化</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>軽量CT+5%</t>
         </is>
       </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>重量</t>
         </is>
       </c>
-      <c r="O27" s="2" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>PRT027</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>反射腕・極</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>腕</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>反撃</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>防御</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>防御UP</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
         <is>
           <t>カウンター強化</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
         <is>
           <t>特定条件で戦闘ルールを変更</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
         <is>
           <t>反撃</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>PRT028</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>多腕・零</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>腕</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>多腕</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>多段</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>通常攻撃+1Hit</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
         <is>
           <t>連撃強化</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
         <is>
           <t>特定条件で戦闘ルールを変更</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr"/>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
         <is>
           <t>多腕</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>PRT029</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>俊足脚</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>脚</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>足</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>多脚</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>高速</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>速度UP</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>全CT-5%</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
         <is>
           <t>速撃強化</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
         <is>
           <t>高速</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>PRT030</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>六節脚</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>脚</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>足</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>多脚</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>高速</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>速度UP</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>軽量CT-8%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
         <is>
           <t>待機強化</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
         <is>
           <t>高速</t>
         </is>
       </c>
-      <c r="O31" s="2" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>PRT031</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>重装脚</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>脚</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>足</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>重量</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>防御</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>防御UP</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>重量CT-12%</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
         <is>
           <t>高速CT+8%</t>
         </is>
       </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>重量</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>PRT032</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>俊足脚・改</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>脚</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>足</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>多脚</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>高速</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>速度UP</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>全CT-5%</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
         <is>
           <t>速撃強化</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
         <is>
           <t>同タグ部位2個以上で効果強化</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr"/>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
         <is>
           <t>高速</t>
         </is>
       </c>
-      <c r="O33" s="2" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>PRT033</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>六節脚・異</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>脚</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>足</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>多脚</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>高速</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>速度UP</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>軽量CT-8%</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
         <is>
           <t>待機強化</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
         <is>
           <t>同タグ部位2個以上で効果強化</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr"/>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
         <is>
           <t>高速</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>PRT034</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>重装脚・極</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>脚</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>足</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>重量</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>防御</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>防御UP</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>重量CT-12%</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-      <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
         <is>
           <t>特定条件で戦闘ルールを変更</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>高速CT+8%</t>
         </is>
       </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>重量</t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>PRT035</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>俊足脚・零</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>脚</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>足</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>多脚</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>高速</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>速度UP</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>全CT-5%</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
         <is>
           <t>速撃強化</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
         <is>
           <t>特定条件で戦闘ルールを変更</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr"/>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
         <is>
           <t>高速</t>
         </is>
       </c>
-      <c r="O36" s="2" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>PRT036</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>第二心臓</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>心臓</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>コア</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>多心臓</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>MP</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>最大HPUP</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr"/>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
         <is>
           <t>手番MP+3</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr"/>
-      <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="2" t="inlineStr"/>
-      <c r="M37" s="2" t="inlineStr"/>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
         <is>
           <t>MP循環</t>
         </is>
       </c>
-      <c r="O37" s="2" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>PRT037</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>暴走心臓</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>心臓</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>コア</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>暴走</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>高速</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>低HP攻撃UP</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>HP50%以下CT-15%</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>低HP時MP+2</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr"/>
-      <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr"/>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
         <is>
           <t>暴走</t>
         </is>
       </c>
-      <c r="O38" s="2" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>PRT038</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>魔導心臓</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>心臓</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>コア</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>MP</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>知性</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
         <is>
           <t>最大MP+20/手番MP+1</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>MP技威力+10%</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="2" t="inlineStr"/>
-      <c r="M39" s="2" t="inlineStr"/>
-      <c r="N39" s="2" t="inlineStr">
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
         <is>
           <t>MP</t>
         </is>
       </c>
-      <c r="O39" s="2" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>PRT039</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>第二心臓・改</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>心臓</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>コア</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>多心臓</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>MP</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>最大HPUP</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
         <is>
           <t>手番MP+3</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr"/>
-      <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="2" t="inlineStr">
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
         <is>
           <t>同タグ部位2個以上で効果強化</t>
         </is>
       </c>
-      <c r="M40" s="2" t="inlineStr"/>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
         <is>
           <t>MP循環</t>
         </is>
       </c>
-      <c r="O40" s="2" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>PRT040</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>暴走心臓・異</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>心臓</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>コア</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>暴走</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>高速</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>低HP攻撃UP</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>HP50%以下CT-15%</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>低HP時MP+2</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="inlineStr">
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
         <is>
           <t>同タグ部位2個以上で効果強化</t>
         </is>
       </c>
-      <c r="M41" s="2" t="inlineStr"/>
-      <c r="N41" s="2" t="inlineStr">
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
         <is>
           <t>暴走</t>
         </is>
       </c>
-      <c r="O41" s="2" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>PRT041</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>魔導心臓・極</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>心臓</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>コア</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>MP</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>知性</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
         <is>
           <t>最大MP+20/手番MP+1</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>MP技威力+10%</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr">
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
         <is>
           <t>特定条件で戦闘ルールを変更</t>
         </is>
       </c>
-      <c r="M42" s="2" t="inlineStr"/>
-      <c r="N42" s="2" t="inlineStr">
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
         <is>
           <t>MP</t>
         </is>
       </c>
-      <c r="O42" s="2" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>PRT042</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>第二心臓・零</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>心臓</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>コア</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>多心臓</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>MP</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>最大HPUP</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr"/>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
         <is>
           <t>手番MP+3</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr"/>
-      <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="2" t="inlineStr">
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
         <is>
           <t>特定条件で戦闘ルールを変更</t>
         </is>
       </c>
-      <c r="M43" s="2" t="inlineStr"/>
-      <c r="N43" s="2" t="inlineStr">
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
         <is>
           <t>MP循環</t>
         </is>
       </c>
-      <c r="O43" s="2" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>PRT043</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>巨殻</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>胴</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>体</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>防御</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>重量</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>防御大UP</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>全CT+8%</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
         <is>
           <t>防御強化</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="inlineStr"/>
-      <c r="M44" s="2" t="inlineStr">
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
         <is>
           <t>速度低下</t>
         </is>
       </c>
-      <c r="N44" s="2" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>タンク</t>
         </is>
       </c>
-      <c r="O44" s="2" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>PRT044</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>再生胴</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>胴</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>体</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>再生</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>防御</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>HP再生</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr"/>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
         <is>
           <t>再生系強化</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="2" t="inlineStr"/>
-      <c r="M45" s="2" t="inlineStr"/>
-      <c r="N45" s="2" t="inlineStr">
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
         <is>
           <t>耐久</t>
         </is>
       </c>
-      <c r="O45" s="2" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>PRT045</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>棘甲</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>胴</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>体</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>反撃</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>防御</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>被弾時反射</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr"/>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
         <is>
           <t>棘返し強化</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="inlineStr"/>
-      <c r="M46" s="2" t="inlineStr"/>
-      <c r="N46" s="2" t="inlineStr">
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
         <is>
           <t>反撃</t>
         </is>
       </c>
-      <c r="O46" s="2" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>PRT046</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>巨殻・改</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>胴</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>体</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>防御</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>重量</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>防御大UP</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>全CT+8%</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
         <is>
           <t>防御強化</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr"/>
-      <c r="L47" s="2" t="inlineStr">
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
         <is>
           <t>同タグ部位2個以上で効果強化</t>
         </is>
       </c>
-      <c r="M47" s="2" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>速度低下</t>
         </is>
       </c>
-      <c r="N47" s="2" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>タンク</t>
         </is>
       </c>
-      <c r="O47" s="2" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>PRT047</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>再生胴・異</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>胴</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>体</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>再生</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>防御</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>HP再生</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr">
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
         <is>
           <t>再生系強化</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="inlineStr">
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
         <is>
           <t>同タグ部位2個以上で効果強化</t>
         </is>
       </c>
-      <c r="M48" s="2" t="inlineStr"/>
-      <c r="N48" s="2" t="inlineStr">
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
         <is>
           <t>耐久</t>
         </is>
       </c>
-      <c r="O48" s="2" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>PRT048</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>棘甲・極</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>胴</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>体</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>反撃</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>防御</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>被弾時反射</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr"/>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr">
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
         <is>
           <t>棘返し強化</t>
         </is>
       </c>
-      <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="2" t="inlineStr">
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
         <is>
           <t>特定条件で戦闘ルールを変更</t>
         </is>
       </c>
-      <c r="M49" s="2" t="inlineStr"/>
-      <c r="N49" s="2" t="inlineStr">
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
         <is>
           <t>反撃</t>
         </is>
       </c>
-      <c r="O49" s="2" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>PRT049</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>巨殻・零</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>胴</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>体</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>防御</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>重量</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>防御大UP</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>全CT+8%</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
         <is>
           <t>防御強化</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="2" t="inlineStr">
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
         <is>
           <t>特定条件で戦闘ルールを変更</t>
         </is>
       </c>
-      <c r="M50" s="2" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>速度低下</t>
         </is>
       </c>
-      <c r="N50" s="2" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>タンク</t>
         </is>
       </c>
-      <c r="O50" s="2" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>PRT050</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>反撃尾</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>尻尾</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>反撃</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>高速</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
         <is>
           <t>被弾後割込率UP</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr">
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
         <is>
           <t>カウンター強化</t>
         </is>
       </c>
-      <c r="K51" s="2" t="inlineStr"/>
-      <c r="L51" s="2" t="inlineStr"/>
-      <c r="M51" s="2" t="inlineStr"/>
-      <c r="N51" s="2" t="inlineStr">
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
         <is>
           <t>反撃</t>
         </is>
       </c>
-      <c r="O51" s="2" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>PRT051</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>毒尾</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>尻尾</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>毒</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>状態異常</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr"/>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr">
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
         <is>
           <t>攻撃に毒付与</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>毒</t>
         </is>
       </c>
-      <c r="L52" s="2" t="inlineStr"/>
-      <c r="M52" s="2" t="inlineStr"/>
-      <c r="N52" s="2" t="inlineStr">
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
         <is>
           <t>毒</t>
         </is>
       </c>
-      <c r="O52" s="2" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="A53" t="inlineStr">
         <is>
           <t>PRT052</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>時間尾</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>尻尾</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>時間</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>妨害</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
         <is>
           <t>敵CT遅延+10%</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr">
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
         <is>
           <t>遅延打撃強化</t>
         </is>
       </c>
-      <c r="K53" s="2" t="inlineStr"/>
-      <c r="L53" s="2" t="inlineStr"/>
-      <c r="M53" s="2" t="inlineStr"/>
-      <c r="N53" s="2" t="inlineStr">
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
         <is>
           <t>CT妨害</t>
         </is>
       </c>
-      <c r="O53" s="2" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="A54" t="inlineStr">
         <is>
           <t>PRT053</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>反撃尾・改</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>尻尾</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>反撃</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>高速</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
         <is>
           <t>被弾後割込率UP</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
         <is>
           <t>カウンター強化</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="2" t="inlineStr">
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
         <is>
           <t>同タグ部位2個以上で効果強化</t>
         </is>
       </c>
-      <c r="M54" s="2" t="inlineStr"/>
-      <c r="N54" s="2" t="inlineStr">
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
         <is>
           <t>反撃</t>
         </is>
       </c>
-      <c r="O54" s="2" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="A55" t="inlineStr">
         <is>
           <t>PRT054</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>毒尾・異</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>尻尾</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>毒</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>状態異常</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr"/>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr">
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
         <is>
           <t>攻撃に毒付与</t>
         </is>
       </c>
-      <c r="K55" s="2" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>毒</t>
         </is>
       </c>
-      <c r="L55" s="2" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>同タグ部位2個以上で効果強化</t>
         </is>
       </c>
-      <c r="M55" s="2" t="inlineStr"/>
-      <c r="N55" s="2" t="inlineStr">
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
         <is>
           <t>毒</t>
         </is>
       </c>
-      <c r="O55" s="2" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="A56" t="inlineStr">
         <is>
           <t>PRT055</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>時間尾・極</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>尻尾</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>時間</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>妨害</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
         <is>
           <t>敵CT遅延+10%</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr">
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
         <is>
           <t>遅延打撃強化</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr"/>
-      <c r="L56" s="2" t="inlineStr">
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
         <is>
           <t>特定条件で戦闘ルールを変更</t>
         </is>
       </c>
-      <c r="M56" s="2" t="inlineStr"/>
-      <c r="N56" s="2" t="inlineStr">
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
         <is>
           <t>CT妨害</t>
         </is>
       </c>
-      <c r="O56" s="2" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="A57" t="inlineStr">
         <is>
           <t>PRT056</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>反撃尾・零</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>尻尾</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>反撃</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>高速</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
         <is>
           <t>被弾後割込率UP</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr">
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
         <is>
           <t>カウンター強化</t>
         </is>
       </c>
-      <c r="K57" s="2" t="inlineStr"/>
-      <c r="L57" s="2" t="inlineStr">
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
         <is>
           <t>特定条件で戦闘ルールを変更</t>
         </is>
       </c>
-      <c r="M57" s="2" t="inlineStr"/>
-      <c r="N57" s="2" t="inlineStr">
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
         <is>
           <t>反撃</t>
         </is>
       </c>
-      <c r="O57" s="2" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="A58" t="inlineStr">
         <is>
           <t>PRT057</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>加速翼</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>羽</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>高速</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>翼</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>回避UP</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>全CT-8%</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>高速</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>PRT058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>雷翼</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>羽</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>雷</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>高速</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>回避UP</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>感電敵へのCT-10%</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>雷技強化</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>雷</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>雷</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>PRT059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>黒翼</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>羽</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>吸血</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>暴走</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>攻撃UP</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>撃破時CT-20%</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>捕食強化</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>防御DOWN</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>捕食</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>PRT060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>加速翼・改</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>羽</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>高速</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>翼</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>回避UP</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>全CT-8%</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>同タグ部位2個以上で効果強化</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>高速</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>PRT061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>雷翼・異</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>羽</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>雷</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>高速</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>回避UP</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>感電敵へのCT-10%</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>雷技強化</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>雷</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>同タグ部位2個以上で効果強化</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>雷</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>PRT062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>黒翼・極</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>羽</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>吸血</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>暴走</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>攻撃UP</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>撃破時CT-20%</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>捕食強化</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>特定条件で戦闘ルールを変更</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>防御DOWN</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>捕食</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>PRT063</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>加速翼・零</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>羽</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>高速</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>翼</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>回避UP</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>全CT-8%</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>特定条件で戦闘ルールを変更</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>高速</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>PRT064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>狂戦士角</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>頭</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>翼</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>回避UP</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>全CT-8%</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-      <c r="K58" s="2" t="inlineStr"/>
-      <c r="L58" s="2" t="inlineStr"/>
-      <c r="M58" s="2" t="inlineStr"/>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
-      <c r="O58" s="2" t="inlineStr">
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>暴走</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>重量</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>攻撃大UP</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>重量CT-5%</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>最大MP-10</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>強打+20%</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>防御DOWN</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>暴走</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>PRT058</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>雷翼</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>翼</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>PRT065</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>穿孔角</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>頭</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>貫通</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>重量</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>防御無視</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>穿孔強化</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>貫通</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>PRT066</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>雷角</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>頭</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
         <is>
           <t>雷</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>回避UP</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>感電敵へのCT-10%</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>雷技強化</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>状態異常</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>攻撃UP</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>雷技感電+1</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
         <is>
           <t>雷</t>
         </is>
       </c>
-      <c r="L59" s="2" t="inlineStr"/>
-      <c r="M59" s="2" t="inlineStr"/>
-      <c r="N59" s="2" t="inlineStr">
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
         <is>
           <t>雷</t>
         </is>
       </c>
-      <c r="O59" s="2" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>PRT059</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>黒翼</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>翼</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>PRT067</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>狂戦士角・改</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>頭</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>暴走</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>重量</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>攻撃大UP</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>重量CT-5%</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>最大MP-10</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>強打+20%</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>同タグ部位2個以上で効果強化</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>防御DOWN</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>暴走</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>PRT068</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>穿孔角・異</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>頭</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>貫通</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>重量</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>防御無視</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>穿孔強化</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>同タグ部位2個以上で効果強化</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>貫通</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>PRT069</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>雷角・極</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>頭</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>雷</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>状態異常</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>攻撃UP</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>雷技感電+1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>雷</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>特定条件で戦闘ルールを変更</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>雷</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>PRT070</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>狂戦士角・零</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>頭</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>暴走</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>重量</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>攻撃大UP</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>重量CT-5%</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>最大MP-10</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>強打+20%</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>特定条件で戦闘ルールを変更</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>防御DOWN</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>暴走</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>PRT071</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>魔力嚢</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>器官</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>最大MP+18</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>PRT072</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>毒嚢</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>吸血</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>暴走</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>攻撃UP</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>撃破時CT-20%</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>捕食強化</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr"/>
-      <c r="L60" s="2" t="inlineStr"/>
-      <c r="M60" s="2" t="inlineStr">
-        <is>
-          <t>防御DOWN</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>捕食</t>
-        </is>
-      </c>
-      <c r="O60" s="2" t="inlineStr">
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>毒</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>器官</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>毒ダメ+25%</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>毒</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>毒</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>PRT060</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>加速翼・改</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>翼</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>PRT073</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>時間嚢</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>時間</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>器官</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>補助CT-8%</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>時間系MP-2</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>CT操作</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>PRT074</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>魔力嚢・改</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>翼</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>回避UP</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>全CT-8%</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-      <c r="K61" s="2" t="inlineStr"/>
-      <c r="L61" s="2" t="inlineStr">
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>器官</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>最大MP+18</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
         <is>
           <t>同タグ部位2個以上で効果強化</t>
         </is>
       </c>
-      <c r="M61" s="2" t="inlineStr"/>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
-      <c r="O61" s="2" t="inlineStr">
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>PRT061</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>雷翼・異</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>翼</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>PRT075</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>毒嚢・異</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>雷</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>回避UP</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>感電敵へのCT-10%</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>雷技強化</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>雷</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr">
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>毒</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>器官</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>毒ダメ+25%</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>毒</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
         <is>
           <t>同タグ部位2個以上で効果強化</t>
         </is>
       </c>
-      <c r="M62" s="2" t="inlineStr"/>
-      <c r="N62" s="2" t="inlineStr">
-        <is>
-          <t>雷</t>
-        </is>
-      </c>
-      <c r="O62" s="2" t="inlineStr">
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>毒</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>PRT062</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>黒翼・極</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>翼</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>PRT076</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>時間嚢・極</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>吸血</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>暴走</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>攻撃UP</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>撃破時CT-20%</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>捕食強化</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr"/>
-      <c r="L63" s="2" t="inlineStr">
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>時間</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>器官</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>補助CT-8%</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>時間系MP-2</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
         <is>
           <t>特定条件で戦闘ルールを変更</t>
         </is>
       </c>
-      <c r="M63" s="2" t="inlineStr">
-        <is>
-          <t>防御DOWN</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>捕食</t>
-        </is>
-      </c>
-      <c r="O63" s="2" t="inlineStr">
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>CT操作</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>PRT063</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>加速翼・零</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>翼</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>PRT077</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>魔力嚢・零</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>翼</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>回避UP</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>全CT-8%</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-      <c r="K64" s="2" t="inlineStr"/>
-      <c r="L64" s="2" t="inlineStr">
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>器官</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>最大MP+18</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
         <is>
           <t>特定条件で戦闘ルールを変更</t>
         </is>
       </c>
-      <c r="M64" s="2" t="inlineStr"/>
-      <c r="N64" s="2" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
-      <c r="O64" s="2" t="inlineStr">
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>PRT064</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>狂戦士角</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>角</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>PRT078</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ゼロコスト核</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>コア</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>暴走</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>コア</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>戦闘最初のMP技0</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>1戦1回</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>PRT079</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>変異核</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>コア</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>進化</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>コア</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>変異技強化</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>ランダム性</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>変異</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>PRT080</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>連鎖核</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>コア</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>多段</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>コア</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>追撃時CT-5%</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>多段追撃</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>連撃</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>PRT081</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>分岐骨</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>体</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>コア</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>重量</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>攻撃大UP</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>重量CT-5%</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>最大MP-10</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>強打+20%</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr"/>
-      <c r="L65" s="2" t="inlineStr"/>
-      <c r="M65" s="2" t="inlineStr">
-        <is>
-          <t>防御DOWN</t>
-        </is>
-      </c>
-      <c r="N65" s="2" t="inlineStr">
-        <is>
-          <t>暴走</t>
-        </is>
-      </c>
-      <c r="O65" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>PRT065</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>穿孔角</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>角</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>接続枠+2</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>拡張</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>PRT082</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>増殖核</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>コア</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>貫通</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>重量</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>防御無視</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr"/>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>穿孔強化</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr"/>
-      <c r="L66" s="2" t="inlineStr"/>
-      <c r="M66" s="2" t="inlineStr"/>
-      <c r="N66" s="2" t="inlineStr">
-        <is>
-          <t>貫通</t>
-        </is>
-      </c>
-      <c r="O66" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>PRT066</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>雷角</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>角</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>雷</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>状態異常</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>攻撃UP</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr"/>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>雷技感電+1</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>雷</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr"/>
-      <c r="M67" s="2" t="inlineStr"/>
-      <c r="N67" s="2" t="inlineStr">
-        <is>
-          <t>雷</t>
-        </is>
-      </c>
-      <c r="O67" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>PRT067</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>狂戦士角・改</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>角</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>コア</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>進化</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>最大MP+10</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>接続枠+2</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>拡張</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>PRT083</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>無限枝</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>腕</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>暴走</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>重量</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>攻撃大UP</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>重量CT-5%</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>最大MP-10</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>強打+20%</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr"/>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>同タグ部位2個以上で効果強化</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr">
-        <is>
-          <t>防御DOWN</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="inlineStr">
-        <is>
-          <t>暴走</t>
-        </is>
-      </c>
-      <c r="O68" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>PRT068</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>穿孔角・異</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>角</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>コア</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>多腕</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>接続枠+3</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>速度-4</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>拡張</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>PRT084</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>共生腺</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>貫通</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>重量</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>防御無視</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr"/>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>穿孔強化</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="inlineStr"/>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>同タグ部位2個以上で効果強化</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
-      <c r="N69" s="2" t="inlineStr">
-        <is>
-          <t>貫通</t>
-        </is>
-      </c>
-      <c r="O69" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>PRT069</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>雷角・極</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>角</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>コア</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>再生</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>手番開始時HP+3</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>接続枠+3</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>拡張</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>PRT085</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>原初樹核</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>コア</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>雷</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>状態異常</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>攻撃UP</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr"/>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>雷技感電+1</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>雷</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>特定条件で戦闘ルールを変更</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
-      <c r="N70" s="2" t="inlineStr">
-        <is>
-          <t>雷</t>
-        </is>
-      </c>
-      <c r="O70" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>PRT070</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>狂戦士角・零</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>角</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>Legendary</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>暴走</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>重量</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>攻撃大UP</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>重量CT-5%</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>最大MP-10</t>
-        </is>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>強打+20%</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr"/>
-      <c r="L71" s="2" t="inlineStr">
-        <is>
-          <t>特定条件で戦闘ルールを変更</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr">
-        <is>
-          <t>防御DOWN</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr">
-        <is>
-          <t>暴走</t>
-        </is>
-      </c>
-      <c r="O71" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>PRT071</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>魔力嚢</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>器官</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>MP</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>器官</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr"/>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>最大MP+18</t>
-        </is>
-      </c>
-      <c r="J72" s="2" t="inlineStr"/>
-      <c r="K72" s="2" t="inlineStr"/>
-      <c r="L72" s="2" t="inlineStr"/>
-      <c r="M72" s="2" t="inlineStr"/>
-      <c r="N72" s="2" t="inlineStr">
-        <is>
-          <t>MP</t>
-        </is>
-      </c>
-      <c r="O72" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>PRT072</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>毒嚢</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>器官</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>毒</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>器官</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr"/>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>毒ダメ+25%</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>毒</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr"/>
-      <c r="M73" s="2" t="inlineStr"/>
-      <c r="N73" s="2" t="inlineStr">
-        <is>
-          <t>毒</t>
-        </is>
-      </c>
-      <c r="O73" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>PRT073</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>時間嚢</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>器官</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>時間</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>器官</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>補助CT-8%</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>時間系MP-2</t>
-        </is>
-      </c>
-      <c r="J74" s="2" t="inlineStr"/>
-      <c r="K74" s="2" t="inlineStr"/>
-      <c r="L74" s="2" t="inlineStr"/>
-      <c r="M74" s="2" t="inlineStr"/>
-      <c r="N74" s="2" t="inlineStr">
-        <is>
-          <t>CT操作</t>
-        </is>
-      </c>
-      <c r="O74" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>PRT074</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>魔力嚢・改</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>器官</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>MP</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>器官</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr"/>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>最大MP+18</t>
-        </is>
-      </c>
-      <c r="J75" s="2" t="inlineStr"/>
-      <c r="K75" s="2" t="inlineStr"/>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>同タグ部位2個以上で効果強化</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
-      <c r="N75" s="2" t="inlineStr">
-        <is>
-          <t>MP</t>
-        </is>
-      </c>
-      <c r="O75" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>PRT075</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>毒嚢・異</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>器官</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>毒</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>器官</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr"/>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>毒ダメ+25%</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>毒</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="inlineStr">
-        <is>
-          <t>同タグ部位2個以上で効果強化</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
-      <c r="N76" s="2" t="inlineStr">
-        <is>
-          <t>毒</t>
-        </is>
-      </c>
-      <c r="O76" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>PRT076</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>時間嚢・極</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>器官</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Legendary</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>時間</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>器官</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>補助CT-8%</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>時間系MP-2</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="inlineStr"/>
-      <c r="K77" s="2" t="inlineStr"/>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>特定条件で戦闘ルールを変更</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
-      <c r="N77" s="2" t="inlineStr">
-        <is>
-          <t>CT操作</t>
-        </is>
-      </c>
-      <c r="O77" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>PRT077</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>魔力嚢・零</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>器官</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>Legendary</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>MP</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>器官</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr"/>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>最大MP+18</t>
-        </is>
-      </c>
-      <c r="J78" s="2" t="inlineStr"/>
-      <c r="K78" s="2" t="inlineStr"/>
-      <c r="L78" s="2" t="inlineStr">
-        <is>
-          <t>特定条件で戦闘ルールを変更</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
-      <c r="N78" s="2" t="inlineStr">
-        <is>
-          <t>MP</t>
-        </is>
-      </c>
-      <c r="O78" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>PRT078</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>ゼロコスト核</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>コア</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>MP</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>コア</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr"/>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>戦闘最初のMP技0</t>
-        </is>
-      </c>
-      <c r="J79" s="2" t="inlineStr"/>
-      <c r="K79" s="2" t="inlineStr"/>
-      <c r="L79" s="2" t="inlineStr"/>
-      <c r="M79" s="2" t="inlineStr">
-        <is>
-          <t>1戦1回</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr">
-        <is>
-          <t>MP</t>
-        </is>
-      </c>
-      <c r="O79" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>PRT079</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>変異核</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>コア</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>進化</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>コア</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr"/>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>変異技強化</t>
-        </is>
-      </c>
-      <c r="K80" s="2" t="inlineStr"/>
-      <c r="L80" s="2" t="inlineStr"/>
-      <c r="M80" s="2" t="inlineStr">
-        <is>
-          <t>ランダム性</t>
-        </is>
-      </c>
-      <c r="N80" s="2" t="inlineStr">
-        <is>
-          <t>変異</t>
-        </is>
-      </c>
-      <c r="O80" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>PRT080</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>連鎖核</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>コア</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>多段</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>コア</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>追撃時CT-5%</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>多段追撃</t>
-        </is>
-      </c>
-      <c r="K81" s="2" t="inlineStr"/>
-      <c r="L81" s="2" t="inlineStr"/>
-      <c r="M81" s="2" t="inlineStr"/>
-      <c r="N81" s="2" t="inlineStr">
-        <is>
-          <t>連撃</t>
-        </is>
-      </c>
-      <c r="O81" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>最大HP+20</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>接続枠+4</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>拡張</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O81"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 

--- a/docs/data/chimera_battle_ctb_redesign_v02_clean.xlsx
+++ b/docs/data/chimera_battle_ctb_redesign_v02_clean.xlsx
@@ -926,12 +926,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.95/1.2/1.6/2.05</t>
+          <t>0.9/1.2/1.6/2.05</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.9/1.1/1.4/1.65</t>
+          <t>0.85/1.1/1.4/1.65</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
